--- a/docs/migration-orders/davin-operational-manual/antigravity/migration-process-handbook-antigravity-v13.xlsx
+++ b/docs/migration-orders/davin-operational-manual/antigravity/migration-process-handbook-antigravity-v13.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SaaS Project\trading-alerts-saas-public\docs\migration-orders\davin-operational-manual\antigravity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E0662A8-B4EE-4973-B4DF-C0201BD9A985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D80262EA-21B4-4093-B67A-DE995DC8F8BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7802,7 +7802,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="166">
+  <cellXfs count="167">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -8225,6 +8225,9 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -27928,53 +27931,53 @@
       <c r="S111" s="135"/>
     </row>
     <row r="112" spans="1:19" s="136" customFormat="1" ht="129.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A112" s="161">
+      <c r="A112" s="29">
         <v>121</v>
       </c>
-      <c r="B112" s="162" t="s">
+      <c r="B112" s="132" t="s">
         <v>1401</v>
       </c>
-      <c r="C112" s="162">
+      <c r="C112" s="132">
         <v>101</v>
       </c>
-      <c r="D112" s="163" t="s">
+      <c r="D112" s="133" t="s">
         <v>1402</v>
       </c>
-      <c r="E112" s="164" t="s">
+      <c r="E112" s="134" t="s">
         <v>598</v>
       </c>
-      <c r="F112" s="161" t="s">
+      <c r="F112" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="G112" s="165" t="s">
+      <c r="G112" s="135" t="s">
         <v>2016</v>
       </c>
-      <c r="H112" s="165" t="s">
+      <c r="H112" s="135" t="s">
         <v>2017</v>
       </c>
-      <c r="I112" s="165" t="s">
+      <c r="I112" s="135" t="s">
         <v>1474</v>
       </c>
-      <c r="J112" s="165"/>
-      <c r="K112" s="165" t="s">
+      <c r="J112" s="135"/>
+      <c r="K112" s="135" t="s">
         <v>1475</v>
       </c>
-      <c r="L112" s="165" t="s">
+      <c r="L112" s="135" t="s">
         <v>2018</v>
       </c>
-      <c r="M112" s="164"/>
-      <c r="N112" s="164" t="s">
+      <c r="M112" s="134"/>
+      <c r="N112" s="134" t="s">
         <v>1592</v>
       </c>
-      <c r="O112" s="165" t="s">
+      <c r="O112" s="135" t="s">
         <v>1470</v>
       </c>
-      <c r="P112" s="165"/>
-      <c r="Q112" s="165"/>
-      <c r="R112" s="165" t="s">
+      <c r="P112" s="135"/>
+      <c r="Q112" s="135"/>
+      <c r="R112" s="135" t="s">
         <v>2019</v>
       </c>
-      <c r="S112" s="165"/>
+      <c r="S112" s="135"/>
     </row>
     <row r="113" spans="1:19" s="136" customFormat="1" ht="129.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="29">
@@ -28074,56 +28077,56 @@
       </c>
       <c r="S114" s="135"/>
     </row>
-    <row r="115" spans="1:19" s="136" customFormat="1" ht="129.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A115" s="29">
+    <row r="115" spans="1:19" s="166" customFormat="1" ht="129.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A115" s="161">
         <v>124</v>
       </c>
-      <c r="B115" s="132" t="s">
+      <c r="B115" s="162" t="s">
         <v>1418</v>
       </c>
-      <c r="C115" s="132">
+      <c r="C115" s="162">
         <v>104</v>
       </c>
-      <c r="D115" s="133" t="s">
+      <c r="D115" s="163" t="s">
         <v>1402</v>
       </c>
-      <c r="E115" s="134" t="s">
+      <c r="E115" s="164" t="s">
         <v>604</v>
       </c>
-      <c r="F115" s="29" t="s">
+      <c r="F115" s="161" t="s">
         <v>120</v>
       </c>
-      <c r="G115" s="135" t="s">
+      <c r="G115" s="165" t="s">
         <v>2028</v>
       </c>
-      <c r="H115" s="135" t="s">
+      <c r="H115" s="165" t="s">
         <v>1509</v>
       </c>
-      <c r="I115" s="135" t="s">
+      <c r="I115" s="165" t="s">
         <v>1596</v>
       </c>
-      <c r="J115" s="135" t="s">
+      <c r="J115" s="165" t="s">
         <v>2029</v>
       </c>
-      <c r="K115" s="135"/>
-      <c r="L115" s="135" t="s">
+      <c r="K115" s="165"/>
+      <c r="L115" s="165" t="s">
         <v>2030</v>
       </c>
-      <c r="M115" s="134"/>
-      <c r="N115" s="134" t="s">
+      <c r="M115" s="164"/>
+      <c r="N115" s="164" t="s">
         <v>1592</v>
       </c>
-      <c r="O115" s="135" t="s">
+      <c r="O115" s="165" t="s">
         <v>1470</v>
       </c>
-      <c r="P115" s="135"/>
-      <c r="Q115" s="135" t="s">
+      <c r="P115" s="165"/>
+      <c r="Q115" s="165" t="s">
         <v>2031</v>
       </c>
-      <c r="R115" s="135" t="s">
+      <c r="R115" s="165" t="s">
         <v>2032</v>
       </c>
-      <c r="S115" s="135"/>
+      <c r="S115" s="165"/>
     </row>
     <row r="116" spans="1:19" s="136" customFormat="1" ht="86.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" s="29">
